--- a/data_generation/10_aquatic_toxicity/tebuconazole_aquatic_toxicity.xlsx
+++ b/data_generation/10_aquatic_toxicity/tebuconazole_aquatic_toxicity.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\10_aquatic_toxicity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D5C3D3-4AAF-4034-9B33-756C36C174D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9178E57-942A-4C92-B6A4-2C6E807FBD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-13068" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="825" yWindow="6945" windowWidth="26895" windowHeight="11550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="aquatic_endpoints" sheetId="6" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="90">
   <si>
     <t>Oncorhynchus mykiss</t>
   </si>
@@ -301,6 +301,12 @@
   </si>
   <si>
     <t>mamr</t>
+  </si>
+  <si>
+    <t>mg/kg dw sed</t>
+  </si>
+  <si>
+    <t>EC15</t>
   </si>
 </sst>
 </file>
@@ -667,29 +673,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C316ADCA-0F97-4E34-A600-B1604EAF90B0}">
-  <dimension ref="A1:X43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.453125" defaultRowHeight="15.65" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:X44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.42578125" defaultRowHeight="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="19.7265625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="7.453125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="4" customWidth="1"/>
     <col min="6" max="6" width="12" style="4" customWidth="1"/>
-    <col min="7" max="8" width="9.453125" style="4"/>
-    <col min="9" max="9" width="9.453125" style="4" customWidth="1"/>
-    <col min="10" max="11" width="9.453125" style="4"/>
-    <col min="12" max="12" width="5.54296875" style="4" customWidth="1"/>
-    <col min="13" max="15" width="9.453125" style="4"/>
-    <col min="16" max="16" width="17.453125" style="4" customWidth="1"/>
-    <col min="17" max="17" width="9.453125" style="4"/>
-    <col min="18" max="18" width="14.26953125" style="4" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" style="4" customWidth="1"/>
-    <col min="20" max="20" width="9.453125" style="5"/>
-    <col min="21" max="16384" width="9.453125" style="4"/>
+    <col min="7" max="8" width="9.42578125" style="4"/>
+    <col min="9" max="9" width="9.42578125" style="4" customWidth="1"/>
+    <col min="10" max="11" width="9.42578125" style="4"/>
+    <col min="12" max="12" width="5.5703125" style="4" customWidth="1"/>
+    <col min="13" max="15" width="9.42578125" style="4"/>
+    <col min="16" max="16" width="17.42578125" style="4" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" style="4"/>
+    <col min="18" max="18" width="14.28515625" style="4" customWidth="1"/>
+    <col min="19" max="19" width="13.140625" style="4" customWidth="1"/>
+    <col min="20" max="20" width="9.42578125" style="5"/>
+    <col min="21" max="16384" width="9.42578125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>23</v>
       </c>
@@ -763,7 +769,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>52</v>
       </c>
@@ -829,7 +835,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>52</v>
       </c>
@@ -895,7 +901,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>52</v>
       </c>
@@ -954,7 +960,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>52</v>
       </c>
@@ -1016,7 +1022,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>52</v>
       </c>
@@ -1078,7 +1084,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>52</v>
       </c>
@@ -1138,7 +1144,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>52</v>
       </c>
@@ -1198,7 +1204,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>52</v>
       </c>
@@ -1258,7 +1264,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>52</v>
       </c>
@@ -1315,7 +1321,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>52</v>
       </c>
@@ -1374,7 +1380,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>52</v>
       </c>
@@ -1423,7 +1429,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>52</v>
       </c>
@@ -1472,7 +1478,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>52</v>
       </c>
@@ -1537,7 +1543,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>52</v>
       </c>
@@ -1599,7 +1605,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>52</v>
       </c>
@@ -1655,7 +1661,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>52</v>
       </c>
@@ -1711,7 +1717,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>52</v>
       </c>
@@ -1767,7 +1773,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>52</v>
       </c>
@@ -1815,7 +1821,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>52</v>
       </c>
@@ -1880,7 +1886,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>52</v>
       </c>
@@ -1942,7 +1948,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>52</v>
       </c>
@@ -1950,28 +1956,52 @@
         <v>74</v>
       </c>
       <c r="D22" s="6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="M22" s="9"/>
+        <v>75</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="10">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="N22" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="O22" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="P22" s="13" t="s">
         <v>86</v>
       </c>
       <c r="Q22" s="13">
         <v>74</v>
       </c>
-      <c r="R22" s="3"/>
-      <c r="S22" s="6"/>
+      <c r="R22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S22" s="6">
+        <v>91</v>
+      </c>
       <c r="T22" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>48</v>
@@ -1980,39 +2010,33 @@
         <v>87</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D23" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="F23" s="4" t="s">
+        <v>79</v>
+      </c>
       <c r="G23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M23" s="9">
-        <v>1.96</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>4</v>
+        <v>89</v>
+      </c>
+      <c r="M23" s="10">
+        <v>42.9</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="P23" s="13" t="s">
         <v>86</v>
@@ -2020,17 +2044,13 @@
       <c r="Q23" s="13">
         <v>74</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="S23" s="6">
-        <v>83</v>
-      </c>
+      <c r="R23" s="3"/>
+      <c r="S23" s="6"/>
       <c r="T23" s="3" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>48</v>
@@ -2039,7 +2059,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>52</v>
       </c>
@@ -2056,7 +2076,7 @@
         <v>21</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>3</v>
@@ -2065,7 +2085,7 @@
         <v>55</v>
       </c>
       <c r="M24" s="9">
-        <v>5.3</v>
+        <v>1.96</v>
       </c>
       <c r="N24" s="9" t="s">
         <v>16</v>
@@ -2098,24 +2118,24 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D25" s="6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>3</v>
@@ -2124,13 +2144,13 @@
         <v>55</v>
       </c>
       <c r="M25" s="9">
-        <v>2.83</v>
+        <v>5.3</v>
       </c>
       <c r="N25" s="9" t="s">
         <v>16</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="P25" s="13" t="s">
         <v>86</v>
@@ -2142,7 +2162,7 @@
         <v>54</v>
       </c>
       <c r="S25" s="6">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T25" s="3" t="s">
         <v>10</v>
@@ -2157,7 +2177,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>52</v>
       </c>
@@ -2171,10 +2191,10 @@
         <v>5</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>3</v>
@@ -2183,7 +2203,7 @@
         <v>55</v>
       </c>
       <c r="M26" s="9">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="N26" s="9" t="s">
         <v>16</v>
@@ -2216,27 +2236,24 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D27" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>3</v>
@@ -2245,13 +2262,13 @@
         <v>55</v>
       </c>
       <c r="M27" s="9">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N27" s="9" t="s">
         <v>16</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="P27" s="13" t="s">
         <v>86</v>
@@ -2263,7 +2280,7 @@
         <v>54</v>
       </c>
       <c r="S27" s="6">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>10</v>
@@ -2278,15 +2295,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D28" s="6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>38</v>
@@ -2294,23 +2311,25 @@
       <c r="G28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I28" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="L28" s="7" t="s">
+      <c r="I28" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L28" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M28" s="10">
-        <v>0.46</v>
-      </c>
-      <c r="N28" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="O28" s="10" t="s">
+      <c r="M28" s="9">
+        <v>3</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O28" s="9" t="s">
         <v>39</v>
       </c>
       <c r="P28" s="13" t="s">
@@ -2323,7 +2342,7 @@
         <v>54</v>
       </c>
       <c r="S28" s="6">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T28" s="3" t="s">
         <v>10</v>
@@ -2338,7 +2357,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>52</v>
       </c>
@@ -2346,25 +2365,26 @@
         <v>82</v>
       </c>
       <c r="D29" s="6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>41</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="J29" s="7"/>
       <c r="K29" s="7" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="L29" s="7" t="s">
         <v>55</v>
       </c>
       <c r="M29" s="10">
-        <v>3.5000000000000003E-2</v>
+        <v>0.46</v>
       </c>
       <c r="N29" s="10" t="s">
         <v>16</v>
@@ -2382,7 +2402,7 @@
         <v>54</v>
       </c>
       <c r="S29" s="6">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>10</v>
@@ -2397,18 +2417,66 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D30" s="6"/>
-      <c r="M30" s="9"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="W30" s="3"/>
-      <c r="X30" s="6"/>
-    </row>
-    <row r="31" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" s="6">
+        <v>24</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M30" s="10">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="N30" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="O30" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="P30" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q30" s="13">
+        <v>74</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="S30" s="6">
+        <v>82</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="W30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="X30" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="6"/>
       <c r="M31" s="9"/>
       <c r="Q31" s="6"/>
@@ -2419,41 +2487,52 @@
       <c r="W31" s="3"/>
       <c r="X31" s="6"/>
     </row>
-    <row r="32" spans="1:24" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:24" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D32" s="6"/>
       <c r="M32" s="9"/>
-    </row>
-    <row r="33" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="6"/>
+    </row>
+    <row r="33" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M33" s="9"/>
     </row>
-    <row r="34" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M34" s="9"/>
     </row>
-    <row r="35" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M35" s="9"/>
     </row>
-    <row r="36" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M36" s="9"/>
     </row>
-    <row r="37" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M37" s="9"/>
     </row>
-    <row r="38" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M38" s="9"/>
     </row>
-    <row r="39" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M39" s="9"/>
     </row>
-    <row r="40" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M40" s="9"/>
     </row>
-    <row r="41" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M41" s="9"/>
     </row>
-    <row r="42" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M42" s="9"/>
     </row>
-    <row r="43" spans="13:13" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M43" s="9"/>
+    </row>
+    <row r="44" spans="13:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M44" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
